--- a/bizconfig/static-xlsx/moba/pixel_moba/effect.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/effect.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,8 +655,6 @@
           <t>physical</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -687,8 +685,6 @@
           <t>true</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -714,7 +710,6 @@
           <t>enemy</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>1</v>
       </c>
@@ -748,13 +743,240 @@
           <t>enemy</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6005</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>破甲标记</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>buff_mark</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>armor_break_pct=0.15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6006</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>震荡状态</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>buff_mark</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>duration_ms=3000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6007</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>寒冷</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>buff_slow</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.1;$skill_level.buff_duration_ms</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>magical</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6008</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>冻结</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>buff_stun</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>$skill_level.buff_duration_ms</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>magical</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6009</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>强化普攻</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>buff_mark</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>empower_pct=0.5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6010</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>击飞</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>buff_airborne</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>$skill_level.buff_duration_ms</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
